--- a/public/PCyS.xlsx
+++ b/public/PCyS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JAraya\Desktop\BESS-JGA\AVANCE DE EQUIPOS MONTADOS\NUEVO PUERTO\Avace de comisionados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D6E5B3-AF45-4F87-8E9D-593E7F322C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D847972D-EEDA-4CF6-BA9A-E118B46878FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55DA33B0-6CEC-444C-B830-1E4260D1E1B0}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{55DA33B0-6CEC-444C-B830-1E4260D1E1B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Comisionado CATL" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="58">
   <si>
     <t>POWER BLOCK N°1</t>
   </si>
@@ -207,6 +207,12 @@
   </si>
   <si>
     <t>Leonel Ramirez / Zabala Esteban</t>
+  </si>
+  <si>
+    <t>3 de 3</t>
+  </si>
+  <si>
+    <t>Ramirez Leonel/ Caseres Edgardo</t>
   </si>
 </sst>
 </file>
@@ -445,13 +451,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7C48157D-E60E-43D3-A81B-62C1356C77DB}" name="Tabla1" displayName="Tabla1" ref="B2:I508" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="B2:I508" xr:uid="{7C48157D-E60E-43D3-A81B-62C1356C77DB}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="POWER BLOCK N°7"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B2:I508" xr:uid="{7C48157D-E60E-43D3-A81B-62C1356C77DB}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{0173632D-34D9-4EAA-AC59-47DD4C7EE096}" name="Sector" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{24313FC6-961E-4E5F-8BED-A74AE798AD8B}" name="Descripcion de tareas" dataDxfId="8"/>
@@ -825,7 +825,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
         <v>0</v>
       </c>
@@ -839,7 +839,7 @@
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
     </row>
-    <row r="4" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
@@ -858,7 +858,7 @@
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
     </row>
-    <row r="5" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
@@ -877,7 +877,7 @@
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>0</v>
       </c>
@@ -896,7 +896,7 @@
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>0</v>
       </c>
@@ -915,7 +915,7 @@
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>0</v>
       </c>
@@ -929,7 +929,7 @@
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
     </row>
-    <row r="9" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>0</v>
       </c>
@@ -948,7 +948,7 @@
       <c r="H9" s="9"/>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>0</v>
       </c>
@@ -967,7 +967,7 @@
       <c r="H10" s="9"/>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>0</v>
       </c>
@@ -986,7 +986,7 @@
       <c r="H11" s="9"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
         <v>0</v>
       </c>
@@ -1000,7 +1000,7 @@
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
     </row>
-    <row r="13" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
@@ -1019,7 +1019,7 @@
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>0</v>
       </c>
@@ -1038,7 +1038,7 @@
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1057,7 +1057,7 @@
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>0</v>
       </c>
@@ -1076,7 +1076,7 @@
       <c r="H16" s="9"/>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>0</v>
       </c>
@@ -1095,7 +1095,7 @@
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>0</v>
       </c>
@@ -1114,7 +1114,7 @@
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>0</v>
       </c>
@@ -1133,7 +1133,7 @@
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>0</v>
       </c>
@@ -1152,7 +1152,7 @@
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
     </row>
-    <row r="21" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>0</v>
       </c>
@@ -1171,7 +1171,7 @@
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
     </row>
-    <row r="22" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>0</v>
       </c>
@@ -1190,7 +1190,7 @@
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>0</v>
       </c>
@@ -1209,7 +1209,7 @@
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>0</v>
       </c>
@@ -1228,7 +1228,7 @@
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
         <v>31</v>
       </c>
@@ -1242,7 +1242,7 @@
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
     </row>
-    <row r="26" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>31</v>
       </c>
@@ -1261,7 +1261,7 @@
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>31</v>
       </c>
@@ -1280,7 +1280,7 @@
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
     </row>
-    <row r="28" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>31</v>
       </c>
@@ -1299,7 +1299,7 @@
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
     </row>
-    <row r="29" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>31</v>
       </c>
@@ -1318,7 +1318,7 @@
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
     </row>
-    <row r="30" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="7" t="s">
         <v>31</v>
       </c>
@@ -1332,7 +1332,7 @@
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
     </row>
-    <row r="31" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
         <v>31</v>
       </c>
@@ -1351,7 +1351,7 @@
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
         <v>31</v>
       </c>
@@ -1370,7 +1370,7 @@
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
         <v>31</v>
       </c>
@@ -1389,7 +1389,7 @@
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
     </row>
-    <row r="34" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
         <v>31</v>
       </c>
@@ -1403,7 +1403,7 @@
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
     </row>
-    <row r="35" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>31</v>
       </c>
@@ -1422,7 +1422,7 @@
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
     </row>
-    <row r="36" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
         <v>31</v>
       </c>
@@ -1441,7 +1441,7 @@
       <c r="H36" s="9"/>
       <c r="I36" s="9"/>
     </row>
-    <row r="37" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
@@ -1460,7 +1460,7 @@
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
         <v>31</v>
       </c>
@@ -1479,7 +1479,7 @@
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1498,7 +1498,7 @@
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
         <v>31</v>
       </c>
@@ -1517,7 +1517,7 @@
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
     </row>
-    <row r="41" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
         <v>31</v>
       </c>
@@ -1536,7 +1536,7 @@
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>31</v>
       </c>
@@ -1555,7 +1555,7 @@
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
     </row>
-    <row r="43" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
         <v>31</v>
       </c>
@@ -1574,7 +1574,7 @@
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
     </row>
-    <row r="44" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>31</v>
       </c>
@@ -1593,7 +1593,7 @@
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
     </row>
-    <row r="45" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
         <v>31</v>
       </c>
@@ -1612,7 +1612,7 @@
       <c r="H45" s="9"/>
       <c r="I45" s="9"/>
     </row>
-    <row r="46" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
         <v>31</v>
       </c>
@@ -1631,7 +1631,7 @@
       <c r="H46" s="9"/>
       <c r="I46" s="9"/>
     </row>
-    <row r="47" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
         <v>32</v>
       </c>
@@ -1645,7 +1645,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
         <v>32</v>
       </c>
@@ -1664,7 +1664,7 @@
       <c r="H48" s="9"/>
       <c r="I48" s="9"/>
     </row>
-    <row r="49" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
         <v>32</v>
       </c>
@@ -1683,7 +1683,7 @@
       <c r="H49" s="9"/>
       <c r="I49" s="9"/>
     </row>
-    <row r="50" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>32</v>
       </c>
@@ -1702,7 +1702,7 @@
       <c r="H50" s="9"/>
       <c r="I50" s="9"/>
     </row>
-    <row r="51" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
         <v>32</v>
       </c>
@@ -1721,7 +1721,7 @@
       <c r="H51" s="9"/>
       <c r="I51" s="9"/>
     </row>
-    <row r="52" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B52" s="7" t="s">
         <v>32</v>
       </c>
@@ -1735,7 +1735,7 @@
       <c r="H52" s="8"/>
       <c r="I52" s="8"/>
     </row>
-    <row r="53" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
         <v>32</v>
       </c>
@@ -1754,7 +1754,7 @@
       <c r="H53" s="9"/>
       <c r="I53" s="9"/>
     </row>
-    <row r="54" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
         <v>32</v>
       </c>
@@ -1773,7 +1773,7 @@
       <c r="H54" s="9"/>
       <c r="I54" s="9"/>
     </row>
-    <row r="55" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
         <v>32</v>
       </c>
@@ -1792,7 +1792,7 @@
       <c r="H55" s="9"/>
       <c r="I55" s="9"/>
     </row>
-    <row r="56" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B56" s="7" t="s">
         <v>32</v>
       </c>
@@ -1806,7 +1806,7 @@
       <c r="H56" s="8"/>
       <c r="I56" s="8"/>
     </row>
-    <row r="57" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
         <v>32</v>
       </c>
@@ -1825,7 +1825,7 @@
       <c r="H57" s="9"/>
       <c r="I57" s="9"/>
     </row>
-    <row r="58" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
         <v>32</v>
       </c>
@@ -1844,7 +1844,7 @@
       <c r="H58" s="9"/>
       <c r="I58" s="9"/>
     </row>
-    <row r="59" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
         <v>32</v>
       </c>
@@ -1863,7 +1863,7 @@
       <c r="H59" s="9"/>
       <c r="I59" s="9"/>
     </row>
-    <row r="60" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
         <v>32</v>
       </c>
@@ -1882,7 +1882,7 @@
       <c r="H60" s="9"/>
       <c r="I60" s="9"/>
     </row>
-    <row r="61" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
         <v>32</v>
       </c>
@@ -1901,7 +1901,7 @@
       <c r="H61" s="9"/>
       <c r="I61" s="9"/>
     </row>
-    <row r="62" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
         <v>32</v>
       </c>
@@ -1920,7 +1920,7 @@
       <c r="H62" s="9"/>
       <c r="I62" s="9"/>
     </row>
-    <row r="63" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
         <v>32</v>
       </c>
@@ -1939,7 +1939,7 @@
       <c r="H63" s="9"/>
       <c r="I63" s="9"/>
     </row>
-    <row r="64" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
         <v>32</v>
       </c>
@@ -1958,7 +1958,7 @@
       <c r="H64" s="9"/>
       <c r="I64" s="9"/>
     </row>
-    <row r="65" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
         <v>32</v>
       </c>
@@ -1977,7 +1977,7 @@
       <c r="H65" s="9"/>
       <c r="I65" s="9"/>
     </row>
-    <row r="66" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
         <v>32</v>
       </c>
@@ -1996,7 +1996,7 @@
       <c r="H66" s="9"/>
       <c r="I66" s="9"/>
     </row>
-    <row r="67" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B67" s="1" t="s">
         <v>32</v>
       </c>
@@ -2015,7 +2015,7 @@
       <c r="H67" s="9"/>
       <c r="I67" s="9"/>
     </row>
-    <row r="68" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B68" s="1" t="s">
         <v>32</v>
       </c>
@@ -2034,7 +2034,7 @@
       <c r="H68" s="9"/>
       <c r="I68" s="9"/>
     </row>
-    <row r="69" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B69" s="7" t="s">
         <v>33</v>
       </c>
@@ -2048,7 +2048,7 @@
       <c r="H69" s="8"/>
       <c r="I69" s="8"/>
     </row>
-    <row r="70" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B70" s="1" t="s">
         <v>33</v>
       </c>
@@ -2067,7 +2067,7 @@
       <c r="H70" s="9"/>
       <c r="I70" s="9"/>
     </row>
-    <row r="71" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B71" s="1" t="s">
         <v>33</v>
       </c>
@@ -2086,7 +2086,7 @@
       <c r="H71" s="9"/>
       <c r="I71" s="9"/>
     </row>
-    <row r="72" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B72" s="1" t="s">
         <v>33</v>
       </c>
@@ -2105,7 +2105,7 @@
       <c r="H72" s="9"/>
       <c r="I72" s="9"/>
     </row>
-    <row r="73" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B73" s="1" t="s">
         <v>33</v>
       </c>
@@ -2124,7 +2124,7 @@
       <c r="H73" s="9"/>
       <c r="I73" s="9"/>
     </row>
-    <row r="74" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B74" s="7" t="s">
         <v>33</v>
       </c>
@@ -2138,7 +2138,7 @@
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
     </row>
-    <row r="75" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B75" s="1" t="s">
         <v>33</v>
       </c>
@@ -2157,7 +2157,7 @@
       <c r="H75" s="9"/>
       <c r="I75" s="9"/>
     </row>
-    <row r="76" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
         <v>33</v>
       </c>
@@ -2176,7 +2176,7 @@
       <c r="H76" s="9"/>
       <c r="I76" s="9"/>
     </row>
-    <row r="77" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
         <v>33</v>
       </c>
@@ -2195,7 +2195,7 @@
       <c r="H77" s="9"/>
       <c r="I77" s="9"/>
     </row>
-    <row r="78" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B78" s="7" t="s">
         <v>33</v>
       </c>
@@ -2209,7 +2209,7 @@
       <c r="H78" s="8"/>
       <c r="I78" s="8"/>
     </row>
-    <row r="79" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
         <v>33</v>
       </c>
@@ -2228,7 +2228,7 @@
       <c r="H79" s="9"/>
       <c r="I79" s="9"/>
     </row>
-    <row r="80" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B80" s="1" t="s">
         <v>33</v>
       </c>
@@ -2247,7 +2247,7 @@
       <c r="H80" s="9"/>
       <c r="I80" s="9"/>
     </row>
-    <row r="81" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B81" s="1" t="s">
         <v>33</v>
       </c>
@@ -2266,7 +2266,7 @@
       <c r="H81" s="9"/>
       <c r="I81" s="9"/>
     </row>
-    <row r="82" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B82" s="1" t="s">
         <v>33</v>
       </c>
@@ -2285,7 +2285,7 @@
       <c r="H82" s="9"/>
       <c r="I82" s="9"/>
     </row>
-    <row r="83" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B83" s="1" t="s">
         <v>33</v>
       </c>
@@ -2304,7 +2304,7 @@
       <c r="H83" s="9"/>
       <c r="I83" s="9"/>
     </row>
-    <row r="84" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B84" s="1" t="s">
         <v>33</v>
       </c>
@@ -2323,7 +2323,7 @@
       <c r="H84" s="9"/>
       <c r="I84" s="9"/>
     </row>
-    <row r="85" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B85" s="1" t="s">
         <v>33</v>
       </c>
@@ -2342,7 +2342,7 @@
       <c r="H85" s="9"/>
       <c r="I85" s="9"/>
     </row>
-    <row r="86" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B86" s="1" t="s">
         <v>33</v>
       </c>
@@ -2361,7 +2361,7 @@
       <c r="H86" s="9"/>
       <c r="I86" s="9"/>
     </row>
-    <row r="87" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
         <v>33</v>
       </c>
@@ -2380,7 +2380,7 @@
       <c r="H87" s="9"/>
       <c r="I87" s="9"/>
     </row>
-    <row r="88" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
         <v>33</v>
       </c>
@@ -2399,7 +2399,7 @@
       <c r="H88" s="9"/>
       <c r="I88" s="9"/>
     </row>
-    <row r="89" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B89" s="1" t="s">
         <v>33</v>
       </c>
@@ -2418,7 +2418,7 @@
       <c r="H89" s="9"/>
       <c r="I89" s="9"/>
     </row>
-    <row r="90" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
         <v>33</v>
       </c>
@@ -2437,7 +2437,7 @@
       <c r="H90" s="9"/>
       <c r="I90" s="9"/>
     </row>
-    <row r="91" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B91" s="7" t="s">
         <v>34</v>
       </c>
@@ -2451,7 +2451,7 @@
       <c r="H91" s="8"/>
       <c r="I91" s="8"/>
     </row>
-    <row r="92" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B92" s="1" t="s">
         <v>34</v>
       </c>
@@ -2470,7 +2470,7 @@
       <c r="H92" s="9"/>
       <c r="I92" s="9"/>
     </row>
-    <row r="93" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B93" s="1" t="s">
         <v>34</v>
       </c>
@@ -2489,7 +2489,7 @@
       <c r="H93" s="9"/>
       <c r="I93" s="9"/>
     </row>
-    <row r="94" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B94" s="1" t="s">
         <v>34</v>
       </c>
@@ -2508,7 +2508,7 @@
       <c r="H94" s="9"/>
       <c r="I94" s="9"/>
     </row>
-    <row r="95" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B95" s="1" t="s">
         <v>34</v>
       </c>
@@ -2527,7 +2527,7 @@
       <c r="H95" s="9"/>
       <c r="I95" s="9"/>
     </row>
-    <row r="96" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B96" s="7" t="s">
         <v>34</v>
       </c>
@@ -2541,7 +2541,7 @@
       <c r="H96" s="8"/>
       <c r="I96" s="8"/>
     </row>
-    <row r="97" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B97" s="1" t="s">
         <v>34</v>
       </c>
@@ -2560,7 +2560,7 @@
       <c r="H97" s="9"/>
       <c r="I97" s="9"/>
     </row>
-    <row r="98" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B98" s="1" t="s">
         <v>34</v>
       </c>
@@ -2579,7 +2579,7 @@
       <c r="H98" s="9"/>
       <c r="I98" s="9"/>
     </row>
-    <row r="99" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B99" s="1" t="s">
         <v>34</v>
       </c>
@@ -2598,7 +2598,7 @@
       <c r="H99" s="9"/>
       <c r="I99" s="9"/>
     </row>
-    <row r="100" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B100" s="7" t="s">
         <v>34</v>
       </c>
@@ -2612,7 +2612,7 @@
       <c r="H100" s="8"/>
       <c r="I100" s="8"/>
     </row>
-    <row r="101" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B101" s="1" t="s">
         <v>34</v>
       </c>
@@ -2631,7 +2631,7 @@
       <c r="H101" s="9"/>
       <c r="I101" s="9"/>
     </row>
-    <row r="102" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B102" s="1" t="s">
         <v>34</v>
       </c>
@@ -2650,7 +2650,7 @@
       <c r="H102" s="9"/>
       <c r="I102" s="9"/>
     </row>
-    <row r="103" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B103" s="1" t="s">
         <v>34</v>
       </c>
@@ -2669,7 +2669,7 @@
       <c r="H103" s="9"/>
       <c r="I103" s="9"/>
     </row>
-    <row r="104" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B104" s="1" t="s">
         <v>34</v>
       </c>
@@ -2688,7 +2688,7 @@
       <c r="H104" s="9"/>
       <c r="I104" s="9"/>
     </row>
-    <row r="105" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B105" s="1" t="s">
         <v>34</v>
       </c>
@@ -2707,7 +2707,7 @@
       <c r="H105" s="9"/>
       <c r="I105" s="9"/>
     </row>
-    <row r="106" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B106" s="1" t="s">
         <v>34</v>
       </c>
@@ -2726,7 +2726,7 @@
       <c r="H106" s="9"/>
       <c r="I106" s="9"/>
     </row>
-    <row r="107" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B107" s="1" t="s">
         <v>34</v>
       </c>
@@ -2745,7 +2745,7 @@
       <c r="H107" s="9"/>
       <c r="I107" s="9"/>
     </row>
-    <row r="108" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B108" s="1" t="s">
         <v>34</v>
       </c>
@@ -2764,7 +2764,7 @@
       <c r="H108" s="9"/>
       <c r="I108" s="9"/>
     </row>
-    <row r="109" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B109" s="1" t="s">
         <v>34</v>
       </c>
@@ -2783,7 +2783,7 @@
       <c r="H109" s="9"/>
       <c r="I109" s="9"/>
     </row>
-    <row r="110" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B110" s="1" t="s">
         <v>34</v>
       </c>
@@ -2802,7 +2802,7 @@
       <c r="H110" s="9"/>
       <c r="I110" s="9"/>
     </row>
-    <row r="111" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B111" s="1" t="s">
         <v>34</v>
       </c>
@@ -2821,7 +2821,7 @@
       <c r="H111" s="9"/>
       <c r="I111" s="9"/>
     </row>
-    <row r="112" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B112" s="1" t="s">
         <v>34</v>
       </c>
@@ -2840,7 +2840,7 @@
       <c r="H112" s="9"/>
       <c r="I112" s="9"/>
     </row>
-    <row r="113" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B113" s="7" t="s">
         <v>35</v>
       </c>
@@ -2854,7 +2854,7 @@
       <c r="H113" s="8"/>
       <c r="I113" s="8"/>
     </row>
-    <row r="114" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B114" s="1" t="s">
         <v>35</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="115" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B115" s="1" t="s">
         <v>35</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="116" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B116" s="1" t="s">
         <v>35</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="117" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B117" s="1" t="s">
         <v>35</v>
       </c>
@@ -2954,7 +2954,7 @@
       <c r="H117" s="9"/>
       <c r="I117" s="9"/>
     </row>
-    <row r="118" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B118" s="7" t="s">
         <v>35</v>
       </c>
@@ -2968,7 +2968,7 @@
       <c r="H118" s="8"/>
       <c r="I118" s="8"/>
     </row>
-    <row r="119" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B119" s="1" t="s">
         <v>35</v>
       </c>
@@ -2987,7 +2987,7 @@
       <c r="H119" s="9"/>
       <c r="I119" s="9"/>
     </row>
-    <row r="120" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B120" s="1" t="s">
         <v>35</v>
       </c>
@@ -3006,7 +3006,7 @@
       <c r="H120" s="9"/>
       <c r="I120" s="9"/>
     </row>
-    <row r="121" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B121" s="1" t="s">
         <v>35</v>
       </c>
@@ -3025,7 +3025,7 @@
       <c r="H121" s="9"/>
       <c r="I121" s="9"/>
     </row>
-    <row r="122" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B122" s="7" t="s">
         <v>35</v>
       </c>
@@ -3039,7 +3039,7 @@
       <c r="H122" s="8"/>
       <c r="I122" s="8"/>
     </row>
-    <row r="123" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B123" s="1" t="s">
         <v>35</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="124" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B124" s="1" t="s">
         <v>35</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="125" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B125" s="1" t="s">
         <v>35</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="126" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B126" s="1" t="s">
         <v>35</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="127" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B127" s="1" t="s">
         <v>35</v>
       </c>
@@ -3166,7 +3166,7 @@
       <c r="H127" s="9"/>
       <c r="I127" s="9"/>
     </row>
-    <row r="128" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B128" s="1" t="s">
         <v>35</v>
       </c>
@@ -3185,7 +3185,7 @@
       <c r="H128" s="9"/>
       <c r="I128" s="9"/>
     </row>
-    <row r="129" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B129" s="1" t="s">
         <v>35</v>
       </c>
@@ -3204,7 +3204,7 @@
       <c r="H129" s="9"/>
       <c r="I129" s="9"/>
     </row>
-    <row r="130" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B130" s="1" t="s">
         <v>35</v>
       </c>
@@ -3223,7 +3223,7 @@
       <c r="H130" s="9"/>
       <c r="I130" s="9"/>
     </row>
-    <row r="131" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B131" s="1" t="s">
         <v>35</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="132" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B132" s="1" t="s">
         <v>35</v>
       </c>
@@ -3269,7 +3269,7 @@
       <c r="H132" s="9"/>
       <c r="I132" s="9"/>
     </row>
-    <row r="133" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B133" s="1" t="s">
         <v>35</v>
       </c>
@@ -3288,7 +3288,7 @@
       <c r="H133" s="9"/>
       <c r="I133" s="9"/>
     </row>
-    <row r="134" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B134" s="1" t="s">
         <v>35</v>
       </c>
@@ -3774,7 +3774,7 @@
       <c r="H156" s="9"/>
       <c r="I156" s="9"/>
     </row>
-    <row r="157" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B157" s="7" t="s">
         <v>37</v>
       </c>
@@ -3788,7 +3788,7 @@
       <c r="H157" s="8"/>
       <c r="I157" s="8"/>
     </row>
-    <row r="158" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B158" s="1" t="s">
         <v>37</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="159" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B159" s="1" t="s">
         <v>37</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="160" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B160" s="1" t="s">
         <v>37</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="161" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B161" s="1" t="s">
         <v>37</v>
       </c>
@@ -3888,7 +3888,7 @@
       <c r="H161" s="9"/>
       <c r="I161" s="9"/>
     </row>
-    <row r="162" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B162" s="7" t="s">
         <v>37</v>
       </c>
@@ -3902,7 +3902,7 @@
       <c r="H162" s="8"/>
       <c r="I162" s="8"/>
     </row>
-    <row r="163" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B163" s="1" t="s">
         <v>37</v>
       </c>
@@ -3921,7 +3921,7 @@
       <c r="H163" s="9"/>
       <c r="I163" s="9"/>
     </row>
-    <row r="164" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B164" s="1" t="s">
         <v>37</v>
       </c>
@@ -3940,7 +3940,7 @@
       <c r="H164" s="9"/>
       <c r="I164" s="9"/>
     </row>
-    <row r="165" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B165" s="1" t="s">
         <v>37</v>
       </c>
@@ -3959,7 +3959,7 @@
       <c r="H165" s="9"/>
       <c r="I165" s="9"/>
     </row>
-    <row r="166" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B166" s="7" t="s">
         <v>37</v>
       </c>
@@ -3973,7 +3973,7 @@
       <c r="H166" s="8"/>
       <c r="I166" s="8"/>
     </row>
-    <row r="167" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B167" s="1" t="s">
         <v>37</v>
       </c>
@@ -4000,7 +4000,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="168" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B168" s="1" t="s">
         <v>37</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="169" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B169" s="1" t="s">
         <v>37</v>
       </c>
@@ -4054,7 +4054,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="170" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B170" s="1" t="s">
         <v>37</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="171" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B171" s="1" t="s">
         <v>37</v>
       </c>
@@ -4100,7 +4100,7 @@
       <c r="H171" s="9"/>
       <c r="I171" s="9"/>
     </row>
-    <row r="172" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B172" s="1" t="s">
         <v>37</v>
       </c>
@@ -4119,7 +4119,7 @@
       <c r="H172" s="9"/>
       <c r="I172" s="9"/>
     </row>
-    <row r="173" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B173" s="1" t="s">
         <v>37</v>
       </c>
@@ -4138,7 +4138,7 @@
       <c r="H173" s="9"/>
       <c r="I173" s="9"/>
     </row>
-    <row r="174" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B174" s="1" t="s">
         <v>37</v>
       </c>
@@ -4157,7 +4157,7 @@
       <c r="H174" s="9"/>
       <c r="I174" s="9"/>
     </row>
-    <row r="175" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B175" s="1" t="s">
         <v>37</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="176" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B176" s="1" t="s">
         <v>37</v>
       </c>
@@ -4203,7 +4203,7 @@
       <c r="H176" s="9"/>
       <c r="I176" s="9"/>
     </row>
-    <row r="177" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B177" s="1" t="s">
         <v>37</v>
       </c>
@@ -4222,7 +4222,7 @@
       <c r="H177" s="9"/>
       <c r="I177" s="9"/>
     </row>
-    <row r="178" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B178" s="1" t="s">
         <v>37</v>
       </c>
@@ -4241,7 +4241,7 @@
       <c r="H178" s="9"/>
       <c r="I178" s="9"/>
     </row>
-    <row r="179" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B179" s="7" t="s">
         <v>38</v>
       </c>
@@ -4255,7 +4255,7 @@
       <c r="H179" s="8"/>
       <c r="I179" s="8"/>
     </row>
-    <row r="180" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B180" s="1" t="s">
         <v>38</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="181" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B181" s="1" t="s">
         <v>38</v>
       </c>
@@ -4309,7 +4309,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="182" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B182" s="1" t="s">
         <v>38</v>
       </c>
@@ -4336,7 +4336,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="183" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B183" s="1" t="s">
         <v>38</v>
       </c>
@@ -4355,7 +4355,7 @@
       <c r="H183" s="9"/>
       <c r="I183" s="9"/>
     </row>
-    <row r="184" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B184" s="7" t="s">
         <v>38</v>
       </c>
@@ -4369,7 +4369,7 @@
       <c r="H184" s="8"/>
       <c r="I184" s="8"/>
     </row>
-    <row r="185" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B185" s="1" t="s">
         <v>38</v>
       </c>
@@ -4388,7 +4388,7 @@
       <c r="H185" s="9"/>
       <c r="I185" s="9"/>
     </row>
-    <row r="186" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B186" s="1" t="s">
         <v>38</v>
       </c>
@@ -4407,7 +4407,7 @@
       <c r="H186" s="9"/>
       <c r="I186" s="9"/>
     </row>
-    <row r="187" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B187" s="1" t="s">
         <v>38</v>
       </c>
@@ -4426,7 +4426,7 @@
       <c r="H187" s="9"/>
       <c r="I187" s="9"/>
     </row>
-    <row r="188" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B188" s="7" t="s">
         <v>38</v>
       </c>
@@ -4440,7 +4440,7 @@
       <c r="H188" s="8"/>
       <c r="I188" s="8"/>
     </row>
-    <row r="189" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B189" s="1" t="s">
         <v>38</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="190" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B190" s="1" t="s">
         <v>38</v>
       </c>
@@ -4494,7 +4494,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="191" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B191" s="1" t="s">
         <v>38</v>
       </c>
@@ -4521,7 +4521,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="192" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B192" s="1" t="s">
         <v>38</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="193" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B193" s="1" t="s">
         <v>38</v>
       </c>
@@ -4567,7 +4567,7 @@
       <c r="H193" s="9"/>
       <c r="I193" s="9"/>
     </row>
-    <row r="194" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B194" s="1" t="s">
         <v>38</v>
       </c>
@@ -4586,7 +4586,7 @@
       <c r="H194" s="9"/>
       <c r="I194" s="9"/>
     </row>
-    <row r="195" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B195" s="1" t="s">
         <v>38</v>
       </c>
@@ -4605,7 +4605,7 @@
       <c r="H195" s="9"/>
       <c r="I195" s="9"/>
     </row>
-    <row r="196" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B196" s="1" t="s">
         <v>38</v>
       </c>
@@ -4624,7 +4624,7 @@
       <c r="H196" s="9"/>
       <c r="I196" s="9"/>
     </row>
-    <row r="197" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B197" s="1" t="s">
         <v>38</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="198" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B198" s="1" t="s">
         <v>38</v>
       </c>
@@ -4670,7 +4670,7 @@
       <c r="H198" s="9"/>
       <c r="I198" s="9"/>
     </row>
-    <row r="199" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B199" s="1" t="s">
         <v>38</v>
       </c>
@@ -4689,7 +4689,7 @@
       <c r="H199" s="9"/>
       <c r="I199" s="9"/>
     </row>
-    <row r="200" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B200" s="1" t="s">
         <v>38</v>
       </c>
@@ -4708,7 +4708,7 @@
       <c r="H200" s="9"/>
       <c r="I200" s="9"/>
     </row>
-    <row r="201" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B201" s="7" t="s">
         <v>39</v>
       </c>
@@ -4722,7 +4722,7 @@
       <c r="H201" s="8"/>
       <c r="I201" s="8"/>
     </row>
-    <row r="202" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B202" s="1" t="s">
         <v>39</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="203" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B203" s="1" t="s">
         <v>39</v>
       </c>
@@ -4776,7 +4776,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="204" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B204" s="1" t="s">
         <v>39</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="205" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B205" s="1" t="s">
         <v>39</v>
       </c>
@@ -4822,7 +4822,7 @@
       <c r="H205" s="9"/>
       <c r="I205" s="9"/>
     </row>
-    <row r="206" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B206" s="7" t="s">
         <v>39</v>
       </c>
@@ -4836,7 +4836,7 @@
       <c r="H206" s="8"/>
       <c r="I206" s="8"/>
     </row>
-    <row r="207" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B207" s="1" t="s">
         <v>39</v>
       </c>
@@ -4855,7 +4855,7 @@
       <c r="H207" s="9"/>
       <c r="I207" s="9"/>
     </row>
-    <row r="208" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B208" s="1" t="s">
         <v>39</v>
       </c>
@@ -4874,7 +4874,7 @@
       <c r="H208" s="9"/>
       <c r="I208" s="9"/>
     </row>
-    <row r="209" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B209" s="1" t="s">
         <v>39</v>
       </c>
@@ -4893,7 +4893,7 @@
       <c r="H209" s="9"/>
       <c r="I209" s="9"/>
     </row>
-    <row r="210" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B210" s="7" t="s">
         <v>39</v>
       </c>
@@ -4907,7 +4907,7 @@
       <c r="H210" s="8"/>
       <c r="I210" s="8"/>
     </row>
-    <row r="211" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B211" s="1" t="s">
         <v>39</v>
       </c>
@@ -4934,7 +4934,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="212" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B212" s="1" t="s">
         <v>39</v>
       </c>
@@ -4961,7 +4961,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="213" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B213" s="1" t="s">
         <v>39</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="214" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B214" s="1" t="s">
         <v>39</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="215" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B215" s="1" t="s">
         <v>39</v>
       </c>
@@ -5034,7 +5034,7 @@
       <c r="H215" s="9"/>
       <c r="I215" s="9"/>
     </row>
-    <row r="216" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B216" s="1" t="s">
         <v>39</v>
       </c>
@@ -5053,7 +5053,7 @@
       <c r="H216" s="9"/>
       <c r="I216" s="9"/>
     </row>
-    <row r="217" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B217" s="1" t="s">
         <v>39</v>
       </c>
@@ -5072,7 +5072,7 @@
       <c r="H217" s="9"/>
       <c r="I217" s="9"/>
     </row>
-    <row r="218" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B218" s="1" t="s">
         <v>39</v>
       </c>
@@ -5091,7 +5091,7 @@
       <c r="H218" s="9"/>
       <c r="I218" s="9"/>
     </row>
-    <row r="219" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B219" s="1" t="s">
         <v>39</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="220" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B220" s="1" t="s">
         <v>39</v>
       </c>
@@ -5137,7 +5137,7 @@
       <c r="H220" s="9"/>
       <c r="I220" s="9"/>
     </row>
-    <row r="221" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B221" s="1" t="s">
         <v>39</v>
       </c>
@@ -5156,7 +5156,7 @@
       <c r="H221" s="9"/>
       <c r="I221" s="9"/>
     </row>
-    <row r="222" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B222" s="1" t="s">
         <v>39</v>
       </c>
@@ -5175,7 +5175,7 @@
       <c r="H222" s="9"/>
       <c r="I222" s="9"/>
     </row>
-    <row r="223" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B223" s="7" t="s">
         <v>40</v>
       </c>
@@ -5189,7 +5189,7 @@
       <c r="H223" s="8"/>
       <c r="I223" s="8"/>
     </row>
-    <row r="224" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B224" s="1" t="s">
         <v>40</v>
       </c>
@@ -5208,7 +5208,7 @@
       <c r="H224" s="9"/>
       <c r="I224" s="9"/>
     </row>
-    <row r="225" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B225" s="1" t="s">
         <v>40</v>
       </c>
@@ -5227,7 +5227,7 @@
       <c r="H225" s="9"/>
       <c r="I225" s="9"/>
     </row>
-    <row r="226" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B226" s="1" t="s">
         <v>40</v>
       </c>
@@ -5246,7 +5246,7 @@
       <c r="H226" s="9"/>
       <c r="I226" s="9"/>
     </row>
-    <row r="227" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B227" s="1" t="s">
         <v>40</v>
       </c>
@@ -5265,7 +5265,7 @@
       <c r="H227" s="9"/>
       <c r="I227" s="9"/>
     </row>
-    <row r="228" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B228" s="7" t="s">
         <v>40</v>
       </c>
@@ -5279,7 +5279,7 @@
       <c r="H228" s="8"/>
       <c r="I228" s="8"/>
     </row>
-    <row r="229" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B229" s="1" t="s">
         <v>40</v>
       </c>
@@ -5298,7 +5298,7 @@
       <c r="H229" s="9"/>
       <c r="I229" s="9"/>
     </row>
-    <row r="230" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B230" s="1" t="s">
         <v>40</v>
       </c>
@@ -5317,7 +5317,7 @@
       <c r="H230" s="9"/>
       <c r="I230" s="9"/>
     </row>
-    <row r="231" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B231" s="1" t="s">
         <v>40</v>
       </c>
@@ -5336,7 +5336,7 @@
       <c r="H231" s="9"/>
       <c r="I231" s="9"/>
     </row>
-    <row r="232" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B232" s="7" t="s">
         <v>40</v>
       </c>
@@ -5350,7 +5350,7 @@
       <c r="H232" s="8"/>
       <c r="I232" s="8"/>
     </row>
-    <row r="233" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B233" s="1" t="s">
         <v>40</v>
       </c>
@@ -5369,7 +5369,7 @@
       <c r="H233" s="9"/>
       <c r="I233" s="9"/>
     </row>
-    <row r="234" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B234" s="1" t="s">
         <v>40</v>
       </c>
@@ -5388,7 +5388,7 @@
       <c r="H234" s="9"/>
       <c r="I234" s="9"/>
     </row>
-    <row r="235" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B235" s="1" t="s">
         <v>40</v>
       </c>
@@ -5407,7 +5407,7 @@
       <c r="H235" s="9"/>
       <c r="I235" s="9"/>
     </row>
-    <row r="236" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B236" s="1" t="s">
         <v>40</v>
       </c>
@@ -5426,7 +5426,7 @@
       <c r="H236" s="9"/>
       <c r="I236" s="9"/>
     </row>
-    <row r="237" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B237" s="1" t="s">
         <v>40</v>
       </c>
@@ -5445,7 +5445,7 @@
       <c r="H237" s="9"/>
       <c r="I237" s="9"/>
     </row>
-    <row r="238" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B238" s="1" t="s">
         <v>40</v>
       </c>
@@ -5464,7 +5464,7 @@
       <c r="H238" s="9"/>
       <c r="I238" s="9"/>
     </row>
-    <row r="239" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B239" s="1" t="s">
         <v>40</v>
       </c>
@@ -5483,7 +5483,7 @@
       <c r="H239" s="9"/>
       <c r="I239" s="9"/>
     </row>
-    <row r="240" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B240" s="1" t="s">
         <v>40</v>
       </c>
@@ -5502,7 +5502,7 @@
       <c r="H240" s="9"/>
       <c r="I240" s="9"/>
     </row>
-    <row r="241" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B241" s="1" t="s">
         <v>40</v>
       </c>
@@ -5521,7 +5521,7 @@
       <c r="H241" s="9"/>
       <c r="I241" s="9"/>
     </row>
-    <row r="242" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B242" s="1" t="s">
         <v>40</v>
       </c>
@@ -5540,7 +5540,7 @@
       <c r="H242" s="9"/>
       <c r="I242" s="9"/>
     </row>
-    <row r="243" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B243" s="1" t="s">
         <v>40</v>
       </c>
@@ -5559,7 +5559,7 @@
       <c r="H243" s="9"/>
       <c r="I243" s="9"/>
     </row>
-    <row r="244" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B244" s="1" t="s">
         <v>40</v>
       </c>
@@ -5578,7 +5578,7 @@
       <c r="H244" s="9"/>
       <c r="I244" s="9"/>
     </row>
-    <row r="245" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B245" s="7" t="s">
         <v>41</v>
       </c>
@@ -5592,7 +5592,7 @@
       <c r="H245" s="8"/>
       <c r="I245" s="8"/>
     </row>
-    <row r="246" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B246" s="1" t="s">
         <v>41</v>
       </c>
@@ -5611,7 +5611,7 @@
       <c r="H246" s="9"/>
       <c r="I246" s="9"/>
     </row>
-    <row r="247" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B247" s="1" t="s">
         <v>41</v>
       </c>
@@ -5630,7 +5630,7 @@
       <c r="H247" s="9"/>
       <c r="I247" s="9"/>
     </row>
-    <row r="248" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B248" s="1" t="s">
         <v>41</v>
       </c>
@@ -5649,7 +5649,7 @@
       <c r="H248" s="9"/>
       <c r="I248" s="9"/>
     </row>
-    <row r="249" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B249" s="1" t="s">
         <v>41</v>
       </c>
@@ -5668,7 +5668,7 @@
       <c r="H249" s="9"/>
       <c r="I249" s="9"/>
     </row>
-    <row r="250" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B250" s="7" t="s">
         <v>41</v>
       </c>
@@ -5682,7 +5682,7 @@
       <c r="H250" s="8"/>
       <c r="I250" s="8"/>
     </row>
-    <row r="251" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B251" s="1" t="s">
         <v>41</v>
       </c>
@@ -5701,7 +5701,7 @@
       <c r="H251" s="9"/>
       <c r="I251" s="9"/>
     </row>
-    <row r="252" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B252" s="1" t="s">
         <v>41</v>
       </c>
@@ -5720,7 +5720,7 @@
       <c r="H252" s="9"/>
       <c r="I252" s="9"/>
     </row>
-    <row r="253" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B253" s="1" t="s">
         <v>41</v>
       </c>
@@ -5739,7 +5739,7 @@
       <c r="H253" s="9"/>
       <c r="I253" s="9"/>
     </row>
-    <row r="254" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B254" s="7" t="s">
         <v>41</v>
       </c>
@@ -5753,7 +5753,7 @@
       <c r="H254" s="8"/>
       <c r="I254" s="8"/>
     </row>
-    <row r="255" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B255" s="1" t="s">
         <v>41</v>
       </c>
@@ -5772,7 +5772,7 @@
       <c r="H255" s="9"/>
       <c r="I255" s="9"/>
     </row>
-    <row r="256" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B256" s="1" t="s">
         <v>41</v>
       </c>
@@ -5791,7 +5791,7 @@
       <c r="H256" s="9"/>
       <c r="I256" s="9"/>
     </row>
-    <row r="257" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B257" s="1" t="s">
         <v>41</v>
       </c>
@@ -5810,7 +5810,7 @@
       <c r="H257" s="9"/>
       <c r="I257" s="9"/>
     </row>
-    <row r="258" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B258" s="1" t="s">
         <v>41</v>
       </c>
@@ -5829,7 +5829,7 @@
       <c r="H258" s="9"/>
       <c r="I258" s="9"/>
     </row>
-    <row r="259" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B259" s="1" t="s">
         <v>41</v>
       </c>
@@ -5848,7 +5848,7 @@
       <c r="H259" s="9"/>
       <c r="I259" s="9"/>
     </row>
-    <row r="260" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B260" s="1" t="s">
         <v>41</v>
       </c>
@@ -5867,7 +5867,7 @@
       <c r="H260" s="9"/>
       <c r="I260" s="9"/>
     </row>
-    <row r="261" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B261" s="1" t="s">
         <v>41</v>
       </c>
@@ -5886,7 +5886,7 @@
       <c r="H261" s="9"/>
       <c r="I261" s="9"/>
     </row>
-    <row r="262" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B262" s="1" t="s">
         <v>41</v>
       </c>
@@ -5905,7 +5905,7 @@
       <c r="H262" s="9"/>
       <c r="I262" s="9"/>
     </row>
-    <row r="263" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B263" s="1" t="s">
         <v>41</v>
       </c>
@@ -5924,7 +5924,7 @@
       <c r="H263" s="9"/>
       <c r="I263" s="9"/>
     </row>
-    <row r="264" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B264" s="1" t="s">
         <v>41</v>
       </c>
@@ -5943,7 +5943,7 @@
       <c r="H264" s="9"/>
       <c r="I264" s="9"/>
     </row>
-    <row r="265" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B265" s="1" t="s">
         <v>41</v>
       </c>
@@ -5962,7 +5962,7 @@
       <c r="H265" s="9"/>
       <c r="I265" s="9"/>
     </row>
-    <row r="266" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B266" s="1" t="s">
         <v>41</v>
       </c>
@@ -5981,7 +5981,7 @@
       <c r="H266" s="9"/>
       <c r="I266" s="9"/>
     </row>
-    <row r="267" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B267" s="7" t="s">
         <v>42</v>
       </c>
@@ -5995,7 +5995,7 @@
       <c r="H267" s="8"/>
       <c r="I267" s="8"/>
     </row>
-    <row r="268" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B268" s="1" t="s">
         <v>42</v>
       </c>
@@ -6014,7 +6014,7 @@
       <c r="H268" s="9"/>
       <c r="I268" s="9"/>
     </row>
-    <row r="269" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B269" s="1" t="s">
         <v>42</v>
       </c>
@@ -6033,7 +6033,7 @@
       <c r="H269" s="9"/>
       <c r="I269" s="9"/>
     </row>
-    <row r="270" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B270" s="1" t="s">
         <v>42</v>
       </c>
@@ -6052,7 +6052,7 @@
       <c r="H270" s="9"/>
       <c r="I270" s="9"/>
     </row>
-    <row r="271" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B271" s="1" t="s">
         <v>42</v>
       </c>
@@ -6071,7 +6071,7 @@
       <c r="H271" s="9"/>
       <c r="I271" s="9"/>
     </row>
-    <row r="272" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B272" s="7" t="s">
         <v>42</v>
       </c>
@@ -6085,7 +6085,7 @@
       <c r="H272" s="8"/>
       <c r="I272" s="8"/>
     </row>
-    <row r="273" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B273" s="1" t="s">
         <v>42</v>
       </c>
@@ -6104,7 +6104,7 @@
       <c r="H273" s="9"/>
       <c r="I273" s="9"/>
     </row>
-    <row r="274" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B274" s="1" t="s">
         <v>42</v>
       </c>
@@ -6123,7 +6123,7 @@
       <c r="H274" s="9"/>
       <c r="I274" s="9"/>
     </row>
-    <row r="275" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B275" s="1" t="s">
         <v>42</v>
       </c>
@@ -6142,7 +6142,7 @@
       <c r="H275" s="9"/>
       <c r="I275" s="9"/>
     </row>
-    <row r="276" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B276" s="7" t="s">
         <v>42</v>
       </c>
@@ -6156,7 +6156,7 @@
       <c r="H276" s="8"/>
       <c r="I276" s="8"/>
     </row>
-    <row r="277" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B277" s="1" t="s">
         <v>42</v>
       </c>
@@ -6175,7 +6175,7 @@
       <c r="H277" s="9"/>
       <c r="I277" s="9"/>
     </row>
-    <row r="278" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B278" s="1" t="s">
         <v>42</v>
       </c>
@@ -6194,7 +6194,7 @@
       <c r="H278" s="9"/>
       <c r="I278" s="9"/>
     </row>
-    <row r="279" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B279" s="1" t="s">
         <v>42</v>
       </c>
@@ -6213,7 +6213,7 @@
       <c r="H279" s="9"/>
       <c r="I279" s="9"/>
     </row>
-    <row r="280" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B280" s="1" t="s">
         <v>42</v>
       </c>
@@ -6232,7 +6232,7 @@
       <c r="H280" s="9"/>
       <c r="I280" s="9"/>
     </row>
-    <row r="281" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B281" s="1" t="s">
         <v>42</v>
       </c>
@@ -6251,7 +6251,7 @@
       <c r="H281" s="9"/>
       <c r="I281" s="9"/>
     </row>
-    <row r="282" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B282" s="1" t="s">
         <v>42</v>
       </c>
@@ -6270,7 +6270,7 @@
       <c r="H282" s="9"/>
       <c r="I282" s="9"/>
     </row>
-    <row r="283" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B283" s="1" t="s">
         <v>42</v>
       </c>
@@ -6289,7 +6289,7 @@
       <c r="H283" s="9"/>
       <c r="I283" s="9"/>
     </row>
-    <row r="284" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B284" s="1" t="s">
         <v>42</v>
       </c>
@@ -6308,7 +6308,7 @@
       <c r="H284" s="9"/>
       <c r="I284" s="9"/>
     </row>
-    <row r="285" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B285" s="1" t="s">
         <v>42</v>
       </c>
@@ -6327,7 +6327,7 @@
       <c r="H285" s="9"/>
       <c r="I285" s="9"/>
     </row>
-    <row r="286" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B286" s="1" t="s">
         <v>42</v>
       </c>
@@ -6346,7 +6346,7 @@
       <c r="H286" s="9"/>
       <c r="I286" s="9"/>
     </row>
-    <row r="287" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B287" s="1" t="s">
         <v>42</v>
       </c>
@@ -6365,7 +6365,7 @@
       <c r="H287" s="9"/>
       <c r="I287" s="9"/>
     </row>
-    <row r="288" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B288" s="1" t="s">
         <v>42</v>
       </c>
@@ -6384,7 +6384,7 @@
       <c r="H288" s="9"/>
       <c r="I288" s="9"/>
     </row>
-    <row r="289" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B289" s="7" t="s">
         <v>43</v>
       </c>
@@ -6398,7 +6398,7 @@
       <c r="H289" s="8"/>
       <c r="I289" s="8"/>
     </row>
-    <row r="290" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B290" s="1" t="s">
         <v>43</v>
       </c>
@@ -6417,7 +6417,7 @@
       <c r="H290" s="9"/>
       <c r="I290" s="9"/>
     </row>
-    <row r="291" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B291" s="1" t="s">
         <v>43</v>
       </c>
@@ -6436,7 +6436,7 @@
       <c r="H291" s="9"/>
       <c r="I291" s="9"/>
     </row>
-    <row r="292" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B292" s="1" t="s">
         <v>43</v>
       </c>
@@ -6455,7 +6455,7 @@
       <c r="H292" s="9"/>
       <c r="I292" s="9"/>
     </row>
-    <row r="293" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B293" s="1" t="s">
         <v>43</v>
       </c>
@@ -6474,7 +6474,7 @@
       <c r="H293" s="9"/>
       <c r="I293" s="9"/>
     </row>
-    <row r="294" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B294" s="7" t="s">
         <v>43</v>
       </c>
@@ -6488,7 +6488,7 @@
       <c r="H294" s="8"/>
       <c r="I294" s="8"/>
     </row>
-    <row r="295" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B295" s="1" t="s">
         <v>43</v>
       </c>
@@ -6507,7 +6507,7 @@
       <c r="H295" s="9"/>
       <c r="I295" s="9"/>
     </row>
-    <row r="296" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B296" s="1" t="s">
         <v>43</v>
       </c>
@@ -6526,7 +6526,7 @@
       <c r="H296" s="9"/>
       <c r="I296" s="9"/>
     </row>
-    <row r="297" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B297" s="1" t="s">
         <v>43</v>
       </c>
@@ -6545,7 +6545,7 @@
       <c r="H297" s="9"/>
       <c r="I297" s="9"/>
     </row>
-    <row r="298" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B298" s="7" t="s">
         <v>43</v>
       </c>
@@ -6559,7 +6559,7 @@
       <c r="H298" s="8"/>
       <c r="I298" s="8"/>
     </row>
-    <row r="299" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B299" s="1" t="s">
         <v>43</v>
       </c>
@@ -6578,7 +6578,7 @@
       <c r="H299" s="9"/>
       <c r="I299" s="9"/>
     </row>
-    <row r="300" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B300" s="1" t="s">
         <v>43</v>
       </c>
@@ -6597,7 +6597,7 @@
       <c r="H300" s="9"/>
       <c r="I300" s="9"/>
     </row>
-    <row r="301" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B301" s="1" t="s">
         <v>43</v>
       </c>
@@ -6616,7 +6616,7 @@
       <c r="H301" s="9"/>
       <c r="I301" s="9"/>
     </row>
-    <row r="302" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B302" s="1" t="s">
         <v>43</v>
       </c>
@@ -6635,7 +6635,7 @@
       <c r="H302" s="9"/>
       <c r="I302" s="9"/>
     </row>
-    <row r="303" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B303" s="1" t="s">
         <v>43</v>
       </c>
@@ -6654,7 +6654,7 @@
       <c r="H303" s="9"/>
       <c r="I303" s="9"/>
     </row>
-    <row r="304" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B304" s="1" t="s">
         <v>43</v>
       </c>
@@ -6673,7 +6673,7 @@
       <c r="H304" s="9"/>
       <c r="I304" s="9"/>
     </row>
-    <row r="305" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B305" s="1" t="s">
         <v>43</v>
       </c>
@@ -6692,7 +6692,7 @@
       <c r="H305" s="9"/>
       <c r="I305" s="9"/>
     </row>
-    <row r="306" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B306" s="1" t="s">
         <v>43</v>
       </c>
@@ -6711,7 +6711,7 @@
       <c r="H306" s="9"/>
       <c r="I306" s="9"/>
     </row>
-    <row r="307" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B307" s="1" t="s">
         <v>43</v>
       </c>
@@ -6730,7 +6730,7 @@
       <c r="H307" s="9"/>
       <c r="I307" s="9"/>
     </row>
-    <row r="308" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B308" s="1" t="s">
         <v>43</v>
       </c>
@@ -6749,7 +6749,7 @@
       <c r="H308" s="9"/>
       <c r="I308" s="9"/>
     </row>
-    <row r="309" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B309" s="1" t="s">
         <v>43</v>
       </c>
@@ -6768,7 +6768,7 @@
       <c r="H309" s="9"/>
       <c r="I309" s="9"/>
     </row>
-    <row r="310" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B310" s="1" t="s">
         <v>43</v>
       </c>
@@ -6787,7 +6787,7 @@
       <c r="H310" s="9"/>
       <c r="I310" s="9"/>
     </row>
-    <row r="311" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B311" s="7" t="s">
         <v>44</v>
       </c>
@@ -6801,7 +6801,7 @@
       <c r="H311" s="8"/>
       <c r="I311" s="8"/>
     </row>
-    <row r="312" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B312" s="1" t="s">
         <v>44</v>
       </c>
@@ -6820,7 +6820,7 @@
       <c r="H312" s="9"/>
       <c r="I312" s="9"/>
     </row>
-    <row r="313" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B313" s="1" t="s">
         <v>44</v>
       </c>
@@ -6839,7 +6839,7 @@
       <c r="H313" s="9"/>
       <c r="I313" s="9"/>
     </row>
-    <row r="314" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B314" s="1" t="s">
         <v>44</v>
       </c>
@@ -6858,7 +6858,7 @@
       <c r="H314" s="9"/>
       <c r="I314" s="9"/>
     </row>
-    <row r="315" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B315" s="1" t="s">
         <v>44</v>
       </c>
@@ -6877,7 +6877,7 @@
       <c r="H315" s="9"/>
       <c r="I315" s="9"/>
     </row>
-    <row r="316" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B316" s="7" t="s">
         <v>44</v>
       </c>
@@ -6891,7 +6891,7 @@
       <c r="H316" s="8"/>
       <c r="I316" s="8"/>
     </row>
-    <row r="317" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B317" s="1" t="s">
         <v>44</v>
       </c>
@@ -6910,7 +6910,7 @@
       <c r="H317" s="9"/>
       <c r="I317" s="9"/>
     </row>
-    <row r="318" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B318" s="1" t="s">
         <v>44</v>
       </c>
@@ -6929,7 +6929,7 @@
       <c r="H318" s="9"/>
       <c r="I318" s="9"/>
     </row>
-    <row r="319" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B319" s="1" t="s">
         <v>44</v>
       </c>
@@ -6948,7 +6948,7 @@
       <c r="H319" s="9"/>
       <c r="I319" s="9"/>
     </row>
-    <row r="320" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B320" s="7" t="s">
         <v>44</v>
       </c>
@@ -6962,7 +6962,7 @@
       <c r="H320" s="8"/>
       <c r="I320" s="8"/>
     </row>
-    <row r="321" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B321" s="1" t="s">
         <v>44</v>
       </c>
@@ -6981,7 +6981,7 @@
       <c r="H321" s="9"/>
       <c r="I321" s="9"/>
     </row>
-    <row r="322" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B322" s="1" t="s">
         <v>44</v>
       </c>
@@ -7000,7 +7000,7 @@
       <c r="H322" s="9"/>
       <c r="I322" s="9"/>
     </row>
-    <row r="323" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B323" s="1" t="s">
         <v>44</v>
       </c>
@@ -7019,7 +7019,7 @@
       <c r="H323" s="9"/>
       <c r="I323" s="9"/>
     </row>
-    <row r="324" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B324" s="1" t="s">
         <v>44</v>
       </c>
@@ -7038,7 +7038,7 @@
       <c r="H324" s="9"/>
       <c r="I324" s="9"/>
     </row>
-    <row r="325" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B325" s="1" t="s">
         <v>44</v>
       </c>
@@ -7057,7 +7057,7 @@
       <c r="H325" s="9"/>
       <c r="I325" s="9"/>
     </row>
-    <row r="326" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B326" s="1" t="s">
         <v>44</v>
       </c>
@@ -7076,7 +7076,7 @@
       <c r="H326" s="9"/>
       <c r="I326" s="9"/>
     </row>
-    <row r="327" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B327" s="1" t="s">
         <v>44</v>
       </c>
@@ -7095,7 +7095,7 @@
       <c r="H327" s="9"/>
       <c r="I327" s="9"/>
     </row>
-    <row r="328" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B328" s="1" t="s">
         <v>44</v>
       </c>
@@ -7114,7 +7114,7 @@
       <c r="H328" s="9"/>
       <c r="I328" s="9"/>
     </row>
-    <row r="329" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B329" s="1" t="s">
         <v>44</v>
       </c>
@@ -7133,7 +7133,7 @@
       <c r="H329" s="9"/>
       <c r="I329" s="9"/>
     </row>
-    <row r="330" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B330" s="1" t="s">
         <v>44</v>
       </c>
@@ -7152,7 +7152,7 @@
       <c r="H330" s="9"/>
       <c r="I330" s="9"/>
     </row>
-    <row r="331" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B331" s="1" t="s">
         <v>44</v>
       </c>
@@ -7171,7 +7171,7 @@
       <c r="H331" s="9"/>
       <c r="I331" s="9"/>
     </row>
-    <row r="332" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B332" s="1" t="s">
         <v>44</v>
       </c>
@@ -7190,7 +7190,7 @@
       <c r="H332" s="9"/>
       <c r="I332" s="9"/>
     </row>
-    <row r="333" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B333" s="7" t="s">
         <v>45</v>
       </c>
@@ -7204,7 +7204,7 @@
       <c r="H333" s="8"/>
       <c r="I333" s="8"/>
     </row>
-    <row r="334" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B334" s="1" t="s">
         <v>45</v>
       </c>
@@ -7223,7 +7223,7 @@
       <c r="H334" s="9"/>
       <c r="I334" s="9"/>
     </row>
-    <row r="335" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B335" s="1" t="s">
         <v>45</v>
       </c>
@@ -7242,7 +7242,7 @@
       <c r="H335" s="9"/>
       <c r="I335" s="9"/>
     </row>
-    <row r="336" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B336" s="1" t="s">
         <v>45</v>
       </c>
@@ -7261,7 +7261,7 @@
       <c r="H336" s="9"/>
       <c r="I336" s="9"/>
     </row>
-    <row r="337" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B337" s="1" t="s">
         <v>45</v>
       </c>
@@ -7280,7 +7280,7 @@
       <c r="H337" s="9"/>
       <c r="I337" s="9"/>
     </row>
-    <row r="338" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B338" s="7" t="s">
         <v>45</v>
       </c>
@@ -7294,7 +7294,7 @@
       <c r="H338" s="8"/>
       <c r="I338" s="8"/>
     </row>
-    <row r="339" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B339" s="1" t="s">
         <v>45</v>
       </c>
@@ -7313,7 +7313,7 @@
       <c r="H339" s="9"/>
       <c r="I339" s="9"/>
     </row>
-    <row r="340" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B340" s="1" t="s">
         <v>45</v>
       </c>
@@ -7332,7 +7332,7 @@
       <c r="H340" s="9"/>
       <c r="I340" s="9"/>
     </row>
-    <row r="341" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B341" s="1" t="s">
         <v>45</v>
       </c>
@@ -7351,7 +7351,7 @@
       <c r="H341" s="9"/>
       <c r="I341" s="9"/>
     </row>
-    <row r="342" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B342" s="7" t="s">
         <v>45</v>
       </c>
@@ -7365,7 +7365,7 @@
       <c r="H342" s="8"/>
       <c r="I342" s="8"/>
     </row>
-    <row r="343" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B343" s="1" t="s">
         <v>45</v>
       </c>
@@ -7384,7 +7384,7 @@
       <c r="H343" s="9"/>
       <c r="I343" s="9"/>
     </row>
-    <row r="344" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B344" s="1" t="s">
         <v>45</v>
       </c>
@@ -7403,7 +7403,7 @@
       <c r="H344" s="9"/>
       <c r="I344" s="9"/>
     </row>
-    <row r="345" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B345" s="1" t="s">
         <v>45</v>
       </c>
@@ -7422,7 +7422,7 @@
       <c r="H345" s="9"/>
       <c r="I345" s="9"/>
     </row>
-    <row r="346" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B346" s="1" t="s">
         <v>45</v>
       </c>
@@ -7441,7 +7441,7 @@
       <c r="H346" s="9"/>
       <c r="I346" s="9"/>
     </row>
-    <row r="347" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B347" s="1" t="s">
         <v>45</v>
       </c>
@@ -7460,7 +7460,7 @@
       <c r="H347" s="9"/>
       <c r="I347" s="9"/>
     </row>
-    <row r="348" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B348" s="1" t="s">
         <v>45</v>
       </c>
@@ -7479,7 +7479,7 @@
       <c r="H348" s="9"/>
       <c r="I348" s="9"/>
     </row>
-    <row r="349" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B349" s="1" t="s">
         <v>45</v>
       </c>
@@ -7498,7 +7498,7 @@
       <c r="H349" s="9"/>
       <c r="I349" s="9"/>
     </row>
-    <row r="350" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B350" s="1" t="s">
         <v>45</v>
       </c>
@@ -7517,7 +7517,7 @@
       <c r="H350" s="9"/>
       <c r="I350" s="9"/>
     </row>
-    <row r="351" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B351" s="1" t="s">
         <v>45</v>
       </c>
@@ -7536,7 +7536,7 @@
       <c r="H351" s="9"/>
       <c r="I351" s="9"/>
     </row>
-    <row r="352" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B352" s="1" t="s">
         <v>45</v>
       </c>
@@ -7555,7 +7555,7 @@
       <c r="H352" s="9"/>
       <c r="I352" s="9"/>
     </row>
-    <row r="353" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B353" s="1" t="s">
         <v>45</v>
       </c>
@@ -7574,7 +7574,7 @@
       <c r="H353" s="9"/>
       <c r="I353" s="9"/>
     </row>
-    <row r="354" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B354" s="1" t="s">
         <v>45</v>
       </c>
@@ -7593,7 +7593,7 @@
       <c r="H354" s="9"/>
       <c r="I354" s="9"/>
     </row>
-    <row r="355" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B355" s="7" t="s">
         <v>46</v>
       </c>
@@ -7607,7 +7607,7 @@
       <c r="H355" s="8"/>
       <c r="I355" s="8"/>
     </row>
-    <row r="356" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B356" s="1" t="s">
         <v>46</v>
       </c>
@@ -7615,18 +7615,26 @@
         <v>17</v>
       </c>
       <c r="D356" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E356" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F356" s="9"/>
-      <c r="G356" s="9"/>
-      <c r="H356" s="9"/>
-      <c r="I356" s="9"/>
-    </row>
-    <row r="357" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F356" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G356" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H356" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I356" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="357" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B357" s="1" t="s">
         <v>46</v>
       </c>
@@ -7634,18 +7642,26 @@
         <v>18</v>
       </c>
       <c r="D357" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E357" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F357" s="9"/>
-      <c r="G357" s="9"/>
-      <c r="H357" s="9"/>
-      <c r="I357" s="9"/>
-    </row>
-    <row r="358" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F357" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G357" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H357" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I357" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="358" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B358" s="1" t="s">
         <v>46</v>
       </c>
@@ -7653,18 +7669,26 @@
         <v>19</v>
       </c>
       <c r="D358" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E358" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F358" s="9"/>
-      <c r="G358" s="9"/>
-      <c r="H358" s="9"/>
-      <c r="I358" s="9"/>
-    </row>
-    <row r="359" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F358" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G358" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H358" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I358" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="359" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B359" s="1" t="s">
         <v>46</v>
       </c>
@@ -7683,7 +7707,7 @@
       <c r="H359" s="9"/>
       <c r="I359" s="9"/>
     </row>
-    <row r="360" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B360" s="7" t="s">
         <v>46</v>
       </c>
@@ -7697,7 +7721,7 @@
       <c r="H360" s="8"/>
       <c r="I360" s="8"/>
     </row>
-    <row r="361" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B361" s="1" t="s">
         <v>46</v>
       </c>
@@ -7716,7 +7740,7 @@
       <c r="H361" s="9"/>
       <c r="I361" s="9"/>
     </row>
-    <row r="362" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B362" s="1" t="s">
         <v>46</v>
       </c>
@@ -7735,7 +7759,7 @@
       <c r="H362" s="9"/>
       <c r="I362" s="9"/>
     </row>
-    <row r="363" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B363" s="1" t="s">
         <v>46</v>
       </c>
@@ -7754,7 +7778,7 @@
       <c r="H363" s="9"/>
       <c r="I363" s="9"/>
     </row>
-    <row r="364" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B364" s="7" t="s">
         <v>46</v>
       </c>
@@ -7768,7 +7792,7 @@
       <c r="H364" s="8"/>
       <c r="I364" s="8"/>
     </row>
-    <row r="365" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B365" s="1" t="s">
         <v>46</v>
       </c>
@@ -7776,18 +7800,26 @@
         <v>4</v>
       </c>
       <c r="D365" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E365" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F365" s="9"/>
-      <c r="G365" s="9"/>
-      <c r="H365" s="9"/>
-      <c r="I365" s="9"/>
-    </row>
-    <row r="366" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F365" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G365" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H365" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I365" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="366" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B366" s="1" t="s">
         <v>46</v>
       </c>
@@ -7795,18 +7827,26 @@
         <v>5</v>
       </c>
       <c r="D366" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E366" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F366" s="9"/>
-      <c r="G366" s="9"/>
-      <c r="H366" s="9"/>
-      <c r="I366" s="9"/>
-    </row>
-    <row r="367" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F366" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G366" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H366" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I366" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="367" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B367" s="1" t="s">
         <v>46</v>
       </c>
@@ -7814,18 +7854,26 @@
         <v>6</v>
       </c>
       <c r="D367" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E367" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F367" s="9"/>
-      <c r="G367" s="9"/>
-      <c r="H367" s="9"/>
-      <c r="I367" s="9"/>
-    </row>
-    <row r="368" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F367" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G367" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H367" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I367" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="368" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B368" s="1" t="s">
         <v>46</v>
       </c>
@@ -7844,7 +7892,7 @@
       <c r="H368" s="9"/>
       <c r="I368" s="9"/>
     </row>
-    <row r="369" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B369" s="1" t="s">
         <v>46</v>
       </c>
@@ -7863,7 +7911,7 @@
       <c r="H369" s="9"/>
       <c r="I369" s="9"/>
     </row>
-    <row r="370" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B370" s="1" t="s">
         <v>46</v>
       </c>
@@ -7882,7 +7930,7 @@
       <c r="H370" s="9"/>
       <c r="I370" s="9"/>
     </row>
-    <row r="371" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B371" s="1" t="s">
         <v>46</v>
       </c>
@@ -7901,7 +7949,7 @@
       <c r="H371" s="9"/>
       <c r="I371" s="9"/>
     </row>
-    <row r="372" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B372" s="1" t="s">
         <v>46</v>
       </c>
@@ -7920,7 +7968,7 @@
       <c r="H372" s="9"/>
       <c r="I372" s="9"/>
     </row>
-    <row r="373" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B373" s="1" t="s">
         <v>46</v>
       </c>
@@ -7928,18 +7976,26 @@
         <v>12</v>
       </c>
       <c r="D373" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E373" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F373" s="9"/>
-      <c r="G373" s="9"/>
-      <c r="H373" s="9"/>
-      <c r="I373" s="9"/>
-    </row>
-    <row r="374" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F373" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G373" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H373" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I373" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="374" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B374" s="1" t="s">
         <v>46</v>
       </c>
@@ -7958,7 +8014,7 @@
       <c r="H374" s="9"/>
       <c r="I374" s="9"/>
     </row>
-    <row r="375" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B375" s="1" t="s">
         <v>46</v>
       </c>
@@ -7977,7 +8033,7 @@
       <c r="H375" s="9"/>
       <c r="I375" s="9"/>
     </row>
-    <row r="376" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B376" s="1" t="s">
         <v>46</v>
       </c>
@@ -7996,7 +8052,7 @@
       <c r="H376" s="9"/>
       <c r="I376" s="9"/>
     </row>
-    <row r="377" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B377" s="7" t="s">
         <v>47</v>
       </c>
@@ -8010,7 +8066,7 @@
       <c r="H377" s="8"/>
       <c r="I377" s="8"/>
     </row>
-    <row r="378" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B378" s="1" t="s">
         <v>47</v>
       </c>
@@ -8018,18 +8074,26 @@
         <v>17</v>
       </c>
       <c r="D378" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E378" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F378" s="9"/>
-      <c r="G378" s="9"/>
-      <c r="H378" s="9"/>
-      <c r="I378" s="9"/>
-    </row>
-    <row r="379" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F378" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G378" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H378" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I378" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="379" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B379" s="1" t="s">
         <v>47</v>
       </c>
@@ -8037,18 +8101,26 @@
         <v>18</v>
       </c>
       <c r="D379" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E379" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F379" s="9"/>
-      <c r="G379" s="9"/>
-      <c r="H379" s="9"/>
-      <c r="I379" s="9"/>
-    </row>
-    <row r="380" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F379" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G379" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H379" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I379" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="380" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B380" s="1" t="s">
         <v>47</v>
       </c>
@@ -8056,18 +8128,26 @@
         <v>19</v>
       </c>
       <c r="D380" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E380" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F380" s="9"/>
-      <c r="G380" s="9"/>
-      <c r="H380" s="9"/>
-      <c r="I380" s="9"/>
-    </row>
-    <row r="381" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F380" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G380" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H380" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I380" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="381" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B381" s="1" t="s">
         <v>47</v>
       </c>
@@ -8086,7 +8166,7 @@
       <c r="H381" s="9"/>
       <c r="I381" s="9"/>
     </row>
-    <row r="382" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B382" s="7" t="s">
         <v>47</v>
       </c>
@@ -8100,7 +8180,7 @@
       <c r="H382" s="8"/>
       <c r="I382" s="8"/>
     </row>
-    <row r="383" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B383" s="1" t="s">
         <v>47</v>
       </c>
@@ -8119,7 +8199,7 @@
       <c r="H383" s="9"/>
       <c r="I383" s="9"/>
     </row>
-    <row r="384" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B384" s="1" t="s">
         <v>47</v>
       </c>
@@ -8138,7 +8218,7 @@
       <c r="H384" s="9"/>
       <c r="I384" s="9"/>
     </row>
-    <row r="385" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B385" s="1" t="s">
         <v>47</v>
       </c>
@@ -8157,7 +8237,7 @@
       <c r="H385" s="9"/>
       <c r="I385" s="9"/>
     </row>
-    <row r="386" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B386" s="7" t="s">
         <v>47</v>
       </c>
@@ -8171,7 +8251,7 @@
       <c r="H386" s="8"/>
       <c r="I386" s="8"/>
     </row>
-    <row r="387" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B387" s="1" t="s">
         <v>47</v>
       </c>
@@ -8179,18 +8259,26 @@
         <v>4</v>
       </c>
       <c r="D387" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E387" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F387" s="9"/>
-      <c r="G387" s="9"/>
-      <c r="H387" s="9"/>
-      <c r="I387" s="9"/>
-    </row>
-    <row r="388" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F387" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G387" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H387" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I387" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="388" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B388" s="1" t="s">
         <v>47</v>
       </c>
@@ -8198,18 +8286,26 @@
         <v>5</v>
       </c>
       <c r="D388" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E388" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F388" s="9"/>
-      <c r="G388" s="9"/>
-      <c r="H388" s="9"/>
-      <c r="I388" s="9"/>
-    </row>
-    <row r="389" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F388" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G388" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H388" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I388" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="389" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B389" s="1" t="s">
         <v>47</v>
       </c>
@@ -8217,18 +8313,26 @@
         <v>6</v>
       </c>
       <c r="D389" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E389" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F389" s="9"/>
-      <c r="G389" s="9"/>
-      <c r="H389" s="9"/>
-      <c r="I389" s="9"/>
-    </row>
-    <row r="390" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F389" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G389" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H389" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I389" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="390" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B390" s="1" t="s">
         <v>47</v>
       </c>
@@ -8247,7 +8351,7 @@
       <c r="H390" s="9"/>
       <c r="I390" s="9"/>
     </row>
-    <row r="391" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B391" s="1" t="s">
         <v>47</v>
       </c>
@@ -8266,7 +8370,7 @@
       <c r="H391" s="9"/>
       <c r="I391" s="9"/>
     </row>
-    <row r="392" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B392" s="1" t="s">
         <v>47</v>
       </c>
@@ -8285,7 +8389,7 @@
       <c r="H392" s="9"/>
       <c r="I392" s="9"/>
     </row>
-    <row r="393" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B393" s="1" t="s">
         <v>47</v>
       </c>
@@ -8304,7 +8408,7 @@
       <c r="H393" s="9"/>
       <c r="I393" s="9"/>
     </row>
-    <row r="394" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B394" s="1" t="s">
         <v>47</v>
       </c>
@@ -8323,7 +8427,7 @@
       <c r="H394" s="9"/>
       <c r="I394" s="9"/>
     </row>
-    <row r="395" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B395" s="1" t="s">
         <v>47</v>
       </c>
@@ -8331,18 +8435,26 @@
         <v>12</v>
       </c>
       <c r="D395" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E395" s="5" t="str">
         <f t="shared" si="10"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F395" s="9"/>
-      <c r="G395" s="9"/>
-      <c r="H395" s="9"/>
-      <c r="I395" s="9"/>
-    </row>
-    <row r="396" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F395" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G395" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H395" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I395" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="396" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B396" s="1" t="s">
         <v>47</v>
       </c>
@@ -8361,7 +8473,7 @@
       <c r="H396" s="9"/>
       <c r="I396" s="9"/>
     </row>
-    <row r="397" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B397" s="1" t="s">
         <v>47</v>
       </c>
@@ -8380,7 +8492,7 @@
       <c r="H397" s="9"/>
       <c r="I397" s="9"/>
     </row>
-    <row r="398" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B398" s="1" t="s">
         <v>47</v>
       </c>
@@ -8399,7 +8511,7 @@
       <c r="H398" s="9"/>
       <c r="I398" s="9"/>
     </row>
-    <row r="399" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B399" s="7" t="s">
         <v>48</v>
       </c>
@@ -8413,7 +8525,7 @@
       <c r="H399" s="8"/>
       <c r="I399" s="8"/>
     </row>
-    <row r="400" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B400" s="1" t="s">
         <v>48</v>
       </c>
@@ -8421,18 +8533,26 @@
         <v>17</v>
       </c>
       <c r="D400" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E400" s="5" t="str">
         <f t="shared" ref="E400:E463" si="12">IF(D400=TRUE," Terminado","Pendiente")</f>
-        <v>Pendiente</v>
-      </c>
-      <c r="F400" s="9"/>
-      <c r="G400" s="9"/>
-      <c r="H400" s="9"/>
-      <c r="I400" s="9"/>
-    </row>
-    <row r="401" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F400" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G400" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H400" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I400" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="401" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B401" s="1" t="s">
         <v>48</v>
       </c>
@@ -8440,18 +8560,26 @@
         <v>18</v>
       </c>
       <c r="D401" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E401" s="5" t="str">
         <f t="shared" si="12"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F401" s="9"/>
-      <c r="G401" s="9"/>
-      <c r="H401" s="9"/>
-      <c r="I401" s="9"/>
-    </row>
-    <row r="402" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F401" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G401" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H401" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I401" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="402" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B402" s="1" t="s">
         <v>48</v>
       </c>
@@ -8459,18 +8587,26 @@
         <v>19</v>
       </c>
       <c r="D402" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E402" s="5" t="str">
         <f t="shared" si="12"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F402" s="9"/>
-      <c r="G402" s="9"/>
-      <c r="H402" s="9"/>
-      <c r="I402" s="9"/>
-    </row>
-    <row r="403" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F402" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G402" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H402" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I402" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="403" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B403" s="1" t="s">
         <v>48</v>
       </c>
@@ -8489,7 +8625,7 @@
       <c r="H403" s="9"/>
       <c r="I403" s="9"/>
     </row>
-    <row r="404" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B404" s="7" t="s">
         <v>48</v>
       </c>
@@ -8503,7 +8639,7 @@
       <c r="H404" s="8"/>
       <c r="I404" s="8"/>
     </row>
-    <row r="405" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B405" s="1" t="s">
         <v>48</v>
       </c>
@@ -8522,7 +8658,7 @@
       <c r="H405" s="9"/>
       <c r="I405" s="9"/>
     </row>
-    <row r="406" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B406" s="1" t="s">
         <v>48</v>
       </c>
@@ -8541,7 +8677,7 @@
       <c r="H406" s="9"/>
       <c r="I406" s="9"/>
     </row>
-    <row r="407" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B407" s="1" t="s">
         <v>48</v>
       </c>
@@ -8560,7 +8696,7 @@
       <c r="H407" s="9"/>
       <c r="I407" s="9"/>
     </row>
-    <row r="408" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B408" s="7" t="s">
         <v>48</v>
       </c>
@@ -8574,7 +8710,7 @@
       <c r="H408" s="8"/>
       <c r="I408" s="8"/>
     </row>
-    <row r="409" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B409" s="1" t="s">
         <v>48</v>
       </c>
@@ -8582,18 +8718,26 @@
         <v>4</v>
       </c>
       <c r="D409" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E409" s="5" t="str">
         <f t="shared" si="12"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F409" s="9"/>
-      <c r="G409" s="9"/>
-      <c r="H409" s="9"/>
-      <c r="I409" s="9"/>
-    </row>
-    <row r="410" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F409" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G409" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H409" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I409" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="410" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B410" s="1" t="s">
         <v>48</v>
       </c>
@@ -8601,18 +8745,26 @@
         <v>5</v>
       </c>
       <c r="D410" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E410" s="5" t="str">
         <f t="shared" si="12"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F410" s="9"/>
-      <c r="G410" s="9"/>
-      <c r="H410" s="9"/>
-      <c r="I410" s="9"/>
-    </row>
-    <row r="411" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F410" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G410" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H410" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I410" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="411" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B411" s="1" t="s">
         <v>48</v>
       </c>
@@ -8620,18 +8772,26 @@
         <v>6</v>
       </c>
       <c r="D411" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E411" s="5" t="str">
         <f t="shared" si="12"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F411" s="9"/>
-      <c r="G411" s="9"/>
-      <c r="H411" s="9"/>
-      <c r="I411" s="9"/>
-    </row>
-    <row r="412" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F411" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G411" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H411" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I411" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="412" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B412" s="1" t="s">
         <v>48</v>
       </c>
@@ -8650,7 +8810,7 @@
       <c r="H412" s="9"/>
       <c r="I412" s="9"/>
     </row>
-    <row r="413" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B413" s="1" t="s">
         <v>48</v>
       </c>
@@ -8669,7 +8829,7 @@
       <c r="H413" s="9"/>
       <c r="I413" s="9"/>
     </row>
-    <row r="414" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B414" s="1" t="s">
         <v>48</v>
       </c>
@@ -8688,7 +8848,7 @@
       <c r="H414" s="9"/>
       <c r="I414" s="9"/>
     </row>
-    <row r="415" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B415" s="1" t="s">
         <v>48</v>
       </c>
@@ -8707,7 +8867,7 @@
       <c r="H415" s="9"/>
       <c r="I415" s="9"/>
     </row>
-    <row r="416" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B416" s="1" t="s">
         <v>48</v>
       </c>
@@ -8726,7 +8886,7 @@
       <c r="H416" s="9"/>
       <c r="I416" s="9"/>
     </row>
-    <row r="417" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B417" s="1" t="s">
         <v>48</v>
       </c>
@@ -8734,18 +8894,26 @@
         <v>12</v>
       </c>
       <c r="D417" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E417" s="5" t="str">
         <f t="shared" si="12"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F417" s="9"/>
-      <c r="G417" s="9"/>
-      <c r="H417" s="9"/>
-      <c r="I417" s="9"/>
-    </row>
-    <row r="418" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F417" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G417" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H417" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I417" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="418" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B418" s="1" t="s">
         <v>48</v>
       </c>
@@ -8764,7 +8932,7 @@
       <c r="H418" s="9"/>
       <c r="I418" s="9"/>
     </row>
-    <row r="419" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B419" s="1" t="s">
         <v>48</v>
       </c>
@@ -8783,7 +8951,7 @@
       <c r="H419" s="9"/>
       <c r="I419" s="9"/>
     </row>
-    <row r="420" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B420" s="1" t="s">
         <v>48</v>
       </c>
@@ -8802,7 +8970,7 @@
       <c r="H420" s="9"/>
       <c r="I420" s="9"/>
     </row>
-    <row r="421" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B421" s="7" t="s">
         <v>49</v>
       </c>
@@ -8816,7 +8984,7 @@
       <c r="H421" s="8"/>
       <c r="I421" s="8"/>
     </row>
-    <row r="422" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B422" s="1" t="s">
         <v>49</v>
       </c>
@@ -8824,18 +8992,26 @@
         <v>17</v>
       </c>
       <c r="D422" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E422" s="5" t="str">
         <f t="shared" si="12"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F422" s="9"/>
-      <c r="G422" s="9"/>
-      <c r="H422" s="9"/>
-      <c r="I422" s="9"/>
-    </row>
-    <row r="423" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F422" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G422" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H422" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I422" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="423" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B423" s="1" t="s">
         <v>49</v>
       </c>
@@ -8843,18 +9019,26 @@
         <v>18</v>
       </c>
       <c r="D423" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E423" s="5" t="str">
         <f t="shared" si="12"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F423" s="9"/>
-      <c r="G423" s="9"/>
-      <c r="H423" s="9"/>
-      <c r="I423" s="9"/>
-    </row>
-    <row r="424" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F423" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G423" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H423" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I423" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="424" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B424" s="1" t="s">
         <v>49</v>
       </c>
@@ -8862,18 +9046,26 @@
         <v>19</v>
       </c>
       <c r="D424" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E424" s="5" t="str">
         <f t="shared" si="12"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F424" s="9"/>
-      <c r="G424" s="9"/>
-      <c r="H424" s="9"/>
-      <c r="I424" s="9"/>
-    </row>
-    <row r="425" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F424" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G424" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H424" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I424" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="425" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B425" s="1" t="s">
         <v>49</v>
       </c>
@@ -8892,7 +9084,7 @@
       <c r="H425" s="9"/>
       <c r="I425" s="9"/>
     </row>
-    <row r="426" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B426" s="7" t="s">
         <v>49</v>
       </c>
@@ -8906,7 +9098,7 @@
       <c r="H426" s="8"/>
       <c r="I426" s="8"/>
     </row>
-    <row r="427" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B427" s="1" t="s">
         <v>49</v>
       </c>
@@ -8925,7 +9117,7 @@
       <c r="H427" s="9"/>
       <c r="I427" s="9"/>
     </row>
-    <row r="428" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B428" s="1" t="s">
         <v>49</v>
       </c>
@@ -8944,7 +9136,7 @@
       <c r="H428" s="9"/>
       <c r="I428" s="9"/>
     </row>
-    <row r="429" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B429" s="1" t="s">
         <v>49</v>
       </c>
@@ -8963,7 +9155,7 @@
       <c r="H429" s="9"/>
       <c r="I429" s="9"/>
     </row>
-    <row r="430" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B430" s="7" t="s">
         <v>49</v>
       </c>
@@ -8977,7 +9169,7 @@
       <c r="H430" s="8"/>
       <c r="I430" s="8"/>
     </row>
-    <row r="431" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B431" s="1" t="s">
         <v>49</v>
       </c>
@@ -8985,18 +9177,26 @@
         <v>4</v>
       </c>
       <c r="D431" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E431" s="5" t="str">
         <f t="shared" si="12"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F431" s="9"/>
-      <c r="G431" s="9"/>
-      <c r="H431" s="9"/>
-      <c r="I431" s="9"/>
-    </row>
-    <row r="432" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F431" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G431" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H431" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I431" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="432" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B432" s="1" t="s">
         <v>49</v>
       </c>
@@ -9004,18 +9204,26 @@
         <v>5</v>
       </c>
       <c r="D432" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E432" s="5" t="str">
         <f t="shared" si="12"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F432" s="9"/>
-      <c r="G432" s="9"/>
-      <c r="H432" s="9"/>
-      <c r="I432" s="9"/>
-    </row>
-    <row r="433" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F432" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G432" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H432" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I432" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="433" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B433" s="1" t="s">
         <v>49</v>
       </c>
@@ -9023,18 +9231,26 @@
         <v>6</v>
       </c>
       <c r="D433" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E433" s="5" t="str">
         <f t="shared" si="12"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F433" s="9"/>
-      <c r="G433" s="9"/>
-      <c r="H433" s="9"/>
-      <c r="I433" s="9"/>
-    </row>
-    <row r="434" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F433" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G433" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H433" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I433" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="434" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B434" s="1" t="s">
         <v>49</v>
       </c>
@@ -9042,18 +9258,26 @@
         <v>7</v>
       </c>
       <c r="D434" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E434" s="5" t="str">
         <f t="shared" si="12"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F434" s="9"/>
-      <c r="G434" s="9"/>
-      <c r="H434" s="9"/>
-      <c r="I434" s="9"/>
-    </row>
-    <row r="435" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F434" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G434" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H434" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I434" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="435" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B435" s="1" t="s">
         <v>49</v>
       </c>
@@ -9072,7 +9296,7 @@
       <c r="H435" s="9"/>
       <c r="I435" s="9"/>
     </row>
-    <row r="436" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B436" s="1" t="s">
         <v>49</v>
       </c>
@@ -9091,7 +9315,7 @@
       <c r="H436" s="9"/>
       <c r="I436" s="9"/>
     </row>
-    <row r="437" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B437" s="1" t="s">
         <v>49</v>
       </c>
@@ -9110,7 +9334,7 @@
       <c r="H437" s="9"/>
       <c r="I437" s="9"/>
     </row>
-    <row r="438" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B438" s="1" t="s">
         <v>49</v>
       </c>
@@ -9129,7 +9353,7 @@
       <c r="H438" s="9"/>
       <c r="I438" s="9"/>
     </row>
-    <row r="439" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B439" s="1" t="s">
         <v>49</v>
       </c>
@@ -9137,18 +9361,26 @@
         <v>12</v>
       </c>
       <c r="D439" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E439" s="5" t="str">
         <f t="shared" si="12"/>
-        <v>Pendiente</v>
-      </c>
-      <c r="F439" s="9"/>
-      <c r="G439" s="9"/>
-      <c r="H439" s="9"/>
-      <c r="I439" s="9"/>
-    </row>
-    <row r="440" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+        <v xml:space="preserve"> Terminado</v>
+      </c>
+      <c r="F439" s="10">
+        <v>46323</v>
+      </c>
+      <c r="G439" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H439" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="I439" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="440" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B440" s="1" t="s">
         <v>49</v>
       </c>
@@ -9167,7 +9399,7 @@
       <c r="H440" s="9"/>
       <c r="I440" s="9"/>
     </row>
-    <row r="441" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B441" s="1" t="s">
         <v>49</v>
       </c>
@@ -9186,7 +9418,7 @@
       <c r="H441" s="9"/>
       <c r="I441" s="9"/>
     </row>
-    <row r="442" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B442" s="1" t="s">
         <v>49</v>
       </c>
@@ -9205,7 +9437,7 @@
       <c r="H442" s="9"/>
       <c r="I442" s="9"/>
     </row>
-    <row r="443" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B443" s="7" t="s">
         <v>50</v>
       </c>
@@ -9219,7 +9451,7 @@
       <c r="H443" s="8"/>
       <c r="I443" s="8"/>
     </row>
-    <row r="444" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B444" s="1" t="s">
         <v>50</v>
       </c>
@@ -9238,7 +9470,7 @@
       <c r="H444" s="9"/>
       <c r="I444" s="9"/>
     </row>
-    <row r="445" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B445" s="1" t="s">
         <v>50</v>
       </c>
@@ -9257,7 +9489,7 @@
       <c r="H445" s="9"/>
       <c r="I445" s="9"/>
     </row>
-    <row r="446" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B446" s="1" t="s">
         <v>50</v>
       </c>
@@ -9276,7 +9508,7 @@
       <c r="H446" s="9"/>
       <c r="I446" s="9"/>
     </row>
-    <row r="447" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B447" s="1" t="s">
         <v>50</v>
       </c>
@@ -9295,7 +9527,7 @@
       <c r="H447" s="9"/>
       <c r="I447" s="9"/>
     </row>
-    <row r="448" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B448" s="7" t="s">
         <v>50</v>
       </c>
@@ -9309,7 +9541,7 @@
       <c r="H448" s="8"/>
       <c r="I448" s="8"/>
     </row>
-    <row r="449" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B449" s="1" t="s">
         <v>50</v>
       </c>
@@ -9328,7 +9560,7 @@
       <c r="H449" s="9"/>
       <c r="I449" s="9"/>
     </row>
-    <row r="450" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B450" s="1" t="s">
         <v>50</v>
       </c>
@@ -9347,7 +9579,7 @@
       <c r="H450" s="9"/>
       <c r="I450" s="9"/>
     </row>
-    <row r="451" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B451" s="1" t="s">
         <v>50</v>
       </c>
@@ -9366,7 +9598,7 @@
       <c r="H451" s="9"/>
       <c r="I451" s="9"/>
     </row>
-    <row r="452" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B452" s="7" t="s">
         <v>50</v>
       </c>
@@ -9380,7 +9612,7 @@
       <c r="H452" s="8"/>
       <c r="I452" s="8"/>
     </row>
-    <row r="453" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B453" s="1" t="s">
         <v>50</v>
       </c>
@@ -9399,7 +9631,7 @@
       <c r="H453" s="9"/>
       <c r="I453" s="9"/>
     </row>
-    <row r="454" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B454" s="1" t="s">
         <v>50</v>
       </c>
@@ -9418,7 +9650,7 @@
       <c r="H454" s="9"/>
       <c r="I454" s="9"/>
     </row>
-    <row r="455" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B455" s="1" t="s">
         <v>50</v>
       </c>
@@ -9437,7 +9669,7 @@
       <c r="H455" s="9"/>
       <c r="I455" s="9"/>
     </row>
-    <row r="456" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B456" s="1" t="s">
         <v>50</v>
       </c>
@@ -9456,7 +9688,7 @@
       <c r="H456" s="9"/>
       <c r="I456" s="9"/>
     </row>
-    <row r="457" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B457" s="1" t="s">
         <v>50</v>
       </c>
@@ -9475,7 +9707,7 @@
       <c r="H457" s="9"/>
       <c r="I457" s="9"/>
     </row>
-    <row r="458" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B458" s="1" t="s">
         <v>50</v>
       </c>
@@ -9494,7 +9726,7 @@
       <c r="H458" s="9"/>
       <c r="I458" s="9"/>
     </row>
-    <row r="459" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B459" s="1" t="s">
         <v>50</v>
       </c>
@@ -9513,7 +9745,7 @@
       <c r="H459" s="9"/>
       <c r="I459" s="9"/>
     </row>
-    <row r="460" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B460" s="1" t="s">
         <v>50</v>
       </c>
@@ -9532,7 +9764,7 @@
       <c r="H460" s="9"/>
       <c r="I460" s="9"/>
     </row>
-    <row r="461" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B461" s="1" t="s">
         <v>50</v>
       </c>
@@ -9551,7 +9783,7 @@
       <c r="H461" s="9"/>
       <c r="I461" s="9"/>
     </row>
-    <row r="462" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B462" s="1" t="s">
         <v>50</v>
       </c>
@@ -9570,7 +9802,7 @@
       <c r="H462" s="9"/>
       <c r="I462" s="9"/>
     </row>
-    <row r="463" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B463" s="1" t="s">
         <v>50</v>
       </c>
@@ -9589,7 +9821,7 @@
       <c r="H463" s="9"/>
       <c r="I463" s="9"/>
     </row>
-    <row r="464" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B464" s="1" t="s">
         <v>50</v>
       </c>
@@ -9608,7 +9840,7 @@
       <c r="H464" s="9"/>
       <c r="I464" s="9"/>
     </row>
-    <row r="465" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B465" s="7" t="s">
         <v>51</v>
       </c>
@@ -9622,7 +9854,7 @@
       <c r="H465" s="8"/>
       <c r="I465" s="8"/>
     </row>
-    <row r="466" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B466" s="1" t="s">
         <v>51</v>
       </c>
@@ -9641,7 +9873,7 @@
       <c r="H466" s="9"/>
       <c r="I466" s="9"/>
     </row>
-    <row r="467" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B467" s="1" t="s">
         <v>51</v>
       </c>
@@ -9660,7 +9892,7 @@
       <c r="H467" s="9"/>
       <c r="I467" s="9"/>
     </row>
-    <row r="468" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B468" s="1" t="s">
         <v>51</v>
       </c>
@@ -9679,7 +9911,7 @@
       <c r="H468" s="9"/>
       <c r="I468" s="9"/>
     </row>
-    <row r="469" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B469" s="1" t="s">
         <v>51</v>
       </c>
@@ -9698,7 +9930,7 @@
       <c r="H469" s="9"/>
       <c r="I469" s="9"/>
     </row>
-    <row r="470" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B470" s="7" t="s">
         <v>51</v>
       </c>
@@ -9712,7 +9944,7 @@
       <c r="H470" s="8"/>
       <c r="I470" s="8"/>
     </row>
-    <row r="471" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B471" s="1" t="s">
         <v>51</v>
       </c>
@@ -9731,7 +9963,7 @@
       <c r="H471" s="9"/>
       <c r="I471" s="9"/>
     </row>
-    <row r="472" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B472" s="1" t="s">
         <v>51</v>
       </c>
@@ -9750,7 +9982,7 @@
       <c r="H472" s="9"/>
       <c r="I472" s="9"/>
     </row>
-    <row r="473" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B473" s="1" t="s">
         <v>51</v>
       </c>
@@ -9769,7 +10001,7 @@
       <c r="H473" s="9"/>
       <c r="I473" s="9"/>
     </row>
-    <row r="474" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B474" s="7" t="s">
         <v>51</v>
       </c>
@@ -9783,7 +10015,7 @@
       <c r="H474" s="8"/>
       <c r="I474" s="8"/>
     </row>
-    <row r="475" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B475" s="1" t="s">
         <v>51</v>
       </c>
@@ -9802,7 +10034,7 @@
       <c r="H475" s="9"/>
       <c r="I475" s="9"/>
     </row>
-    <row r="476" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B476" s="1" t="s">
         <v>51</v>
       </c>
@@ -9821,7 +10053,7 @@
       <c r="H476" s="9"/>
       <c r="I476" s="9"/>
     </row>
-    <row r="477" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B477" s="1" t="s">
         <v>51</v>
       </c>
@@ -9840,7 +10072,7 @@
       <c r="H477" s="9"/>
       <c r="I477" s="9"/>
     </row>
-    <row r="478" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B478" s="1" t="s">
         <v>51</v>
       </c>
@@ -9859,7 +10091,7 @@
       <c r="H478" s="9"/>
       <c r="I478" s="9"/>
     </row>
-    <row r="479" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B479" s="1" t="s">
         <v>51</v>
       </c>
@@ -9878,7 +10110,7 @@
       <c r="H479" s="9"/>
       <c r="I479" s="9"/>
     </row>
-    <row r="480" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B480" s="1" t="s">
         <v>51</v>
       </c>
@@ -9897,7 +10129,7 @@
       <c r="H480" s="9"/>
       <c r="I480" s="9"/>
     </row>
-    <row r="481" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B481" s="1" t="s">
         <v>51</v>
       </c>
@@ -9916,7 +10148,7 @@
       <c r="H481" s="9"/>
       <c r="I481" s="9"/>
     </row>
-    <row r="482" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B482" s="1" t="s">
         <v>51</v>
       </c>
@@ -9935,7 +10167,7 @@
       <c r="H482" s="9"/>
       <c r="I482" s="9"/>
     </row>
-    <row r="483" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B483" s="1" t="s">
         <v>51</v>
       </c>
@@ -9954,7 +10186,7 @@
       <c r="H483" s="9"/>
       <c r="I483" s="9"/>
     </row>
-    <row r="484" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B484" s="1" t="s">
         <v>51</v>
       </c>
@@ -9973,7 +10205,7 @@
       <c r="H484" s="9"/>
       <c r="I484" s="9"/>
     </row>
-    <row r="485" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B485" s="1" t="s">
         <v>51</v>
       </c>
@@ -9992,7 +10224,7 @@
       <c r="H485" s="9"/>
       <c r="I485" s="9"/>
     </row>
-    <row r="486" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B486" s="1" t="s">
         <v>51</v>
       </c>
@@ -10011,7 +10243,7 @@
       <c r="H486" s="9"/>
       <c r="I486" s="9"/>
     </row>
-    <row r="487" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B487" s="7" t="s">
         <v>52</v>
       </c>
@@ -10025,7 +10257,7 @@
       <c r="H487" s="8"/>
       <c r="I487" s="8"/>
     </row>
-    <row r="488" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B488" s="1" t="s">
         <v>52</v>
       </c>
@@ -10044,7 +10276,7 @@
       <c r="H488" s="9"/>
       <c r="I488" s="9"/>
     </row>
-    <row r="489" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B489" s="1" t="s">
         <v>52</v>
       </c>
@@ -10063,7 +10295,7 @@
       <c r="H489" s="9"/>
       <c r="I489" s="9"/>
     </row>
-    <row r="490" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B490" s="1" t="s">
         <v>52</v>
       </c>
@@ -10082,7 +10314,7 @@
       <c r="H490" s="9"/>
       <c r="I490" s="9"/>
     </row>
-    <row r="491" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B491" s="1" t="s">
         <v>52</v>
       </c>
@@ -10101,7 +10333,7 @@
       <c r="H491" s="9"/>
       <c r="I491" s="9"/>
     </row>
-    <row r="492" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B492" s="7" t="s">
         <v>52</v>
       </c>
@@ -10115,7 +10347,7 @@
       <c r="H492" s="8"/>
       <c r="I492" s="8"/>
     </row>
-    <row r="493" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B493" s="1" t="s">
         <v>52</v>
       </c>
@@ -10134,7 +10366,7 @@
       <c r="H493" s="9"/>
       <c r="I493" s="9"/>
     </row>
-    <row r="494" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B494" s="1" t="s">
         <v>52</v>
       </c>
@@ -10153,7 +10385,7 @@
       <c r="H494" s="9"/>
       <c r="I494" s="9"/>
     </row>
-    <row r="495" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B495" s="1" t="s">
         <v>52</v>
       </c>
@@ -10172,7 +10404,7 @@
       <c r="H495" s="9"/>
       <c r="I495" s="9"/>
     </row>
-    <row r="496" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B496" s="7" t="s">
         <v>52</v>
       </c>
@@ -10186,7 +10418,7 @@
       <c r="H496" s="8"/>
       <c r="I496" s="8"/>
     </row>
-    <row r="497" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B497" s="1" t="s">
         <v>52</v>
       </c>
@@ -10205,7 +10437,7 @@
       <c r="H497" s="9"/>
       <c r="I497" s="9"/>
     </row>
-    <row r="498" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B498" s="1" t="s">
         <v>52</v>
       </c>
@@ -10224,7 +10456,7 @@
       <c r="H498" s="9"/>
       <c r="I498" s="9"/>
     </row>
-    <row r="499" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B499" s="1" t="s">
         <v>52</v>
       </c>
@@ -10243,7 +10475,7 @@
       <c r="H499" s="9"/>
       <c r="I499" s="9"/>
     </row>
-    <row r="500" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B500" s="1" t="s">
         <v>52</v>
       </c>
@@ -10262,7 +10494,7 @@
       <c r="H500" s="9"/>
       <c r="I500" s="9"/>
     </row>
-    <row r="501" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B501" s="1" t="s">
         <v>52</v>
       </c>
@@ -10281,7 +10513,7 @@
       <c r="H501" s="9"/>
       <c r="I501" s="9"/>
     </row>
-    <row r="502" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B502" s="1" t="s">
         <v>52</v>
       </c>
@@ -10300,7 +10532,7 @@
       <c r="H502" s="9"/>
       <c r="I502" s="9"/>
     </row>
-    <row r="503" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B503" s="1" t="s">
         <v>52</v>
       </c>
@@ -10319,7 +10551,7 @@
       <c r="H503" s="9"/>
       <c r="I503" s="9"/>
     </row>
-    <row r="504" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B504" s="1" t="s">
         <v>52</v>
       </c>
@@ -10338,7 +10570,7 @@
       <c r="H504" s="9"/>
       <c r="I504" s="9"/>
     </row>
-    <row r="505" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B505" s="1" t="s">
         <v>52</v>
       </c>
@@ -10357,7 +10589,7 @@
       <c r="H505" s="9"/>
       <c r="I505" s="9"/>
     </row>
-    <row r="506" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B506" s="1" t="s">
         <v>52</v>
       </c>
@@ -10376,7 +10608,7 @@
       <c r="H506" s="9"/>
       <c r="I506" s="9"/>
     </row>
-    <row r="507" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B507" s="1" t="s">
         <v>52</v>
       </c>
@@ -10395,7 +10627,7 @@
       <c r="H507" s="9"/>
       <c r="I507" s="9"/>
     </row>
-    <row r="508" spans="2:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B508" s="1" t="s">
         <v>52</v>
       </c>
